--- a/Dataset/EnglishBH_features.xlsx
+++ b/Dataset/EnglishBH_features.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId3"/>
     <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="Sheet4" sheetId="4" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="45">
   <si>
     <t xml:space="preserve">high</t>
   </si>
@@ -135,19 +136,19 @@
     <t xml:space="preserve">h</t>
   </si>
   <si>
-    <t xml:space="preserve">round</t>
+    <t xml:space="preserve">syllabic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">consonantal</t>
   </si>
   <si>
     <t xml:space="preserve">place</t>
   </si>
   <si>
-    <t xml:space="preserve">strident</t>
+    <t xml:space="preserve">round</t>
   </si>
   <si>
-    <t xml:space="preserve">syllabic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">consonantal</t>
+    <t xml:space="preserve">strident</t>
   </si>
   <si>
     <t xml:space="preserve">+</t>
@@ -255,7 +256,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L27"/>
-  <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="5.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1021" style="0" width="8.36"/>
@@ -1300,14 +1301,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
-  <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:N27"/>
+  <sheetFormatPr defaultColWidth="10.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="5.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="6" style="0" width="10.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="5.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1021" style="0" width="8.36"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="0" t="s">
         <v>0</v>
       </c>
@@ -1315,31 +1316,40 @@
         <v>1</v>
       </c>
       <c r="D1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="0" t="s">
+      <c r="N1" s="0" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
         <v>11</v>
       </c>
@@ -1350,31 +1360,40 @@
         <v>0</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H2" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I2" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="0" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0</v>
+      </c>
+      <c r="L2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
         <v>12</v>
       </c>
@@ -1391,25 +1410,34 @@
         <v>0</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H3" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I3" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="0" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0</v>
+      </c>
+      <c r="L3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
         <v>13</v>
       </c>
@@ -1420,31 +1448,40 @@
         <v>0</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="0" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0</v>
+      </c>
+      <c r="L4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
         <v>14</v>
       </c>
@@ -1461,25 +1498,34 @@
         <v>0</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="0" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0</v>
+      </c>
+      <c r="L5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
         <v>15</v>
       </c>
@@ -1493,28 +1539,37 @@
         <v>1</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K6" s="0" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0</v>
+      </c>
+      <c r="L6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
         <v>16</v>
       </c>
@@ -1525,31 +1580,40 @@
         <v>1</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="0" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0</v>
+      </c>
+      <c r="L7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
         <v>17</v>
       </c>
@@ -1563,28 +1627,37 @@
         <v>1</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="0" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0</v>
+      </c>
+      <c r="L8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
         <v>18</v>
       </c>
@@ -1595,150 +1668,186 @@
         <v>1</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I9" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J9" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="0" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0</v>
+      </c>
+      <c r="L9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F10" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K10" s="0" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
         <v>20</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F11" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="0" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
         <v>21</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F12" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J12" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="0" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0</v>
+      </c>
+      <c r="L12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
         <v>22</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="0" t="n">
         <v>0</v>
@@ -1750,30 +1859,39 @@
         <v>0</v>
       </c>
       <c r="I13" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J13" s="0" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K13" s="0" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
         <v>23</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="0" t="n">
         <v>0</v>
@@ -1785,30 +1903,39 @@
         <v>0</v>
       </c>
       <c r="I14" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J14" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="0" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
         <v>24</v>
       </c>
       <c r="B15" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C15" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="0" t="n">
         <v>0</v>
@@ -1820,182 +1947,227 @@
         <v>0</v>
       </c>
       <c r="I15" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J15" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="0" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0</v>
+      </c>
+      <c r="L15" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
         <v>25</v>
       </c>
       <c r="B16" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C16" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J16" s="0" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K16" s="0" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
         <v>26</v>
       </c>
       <c r="B17" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C17" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J17" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K17" s="0" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
         <v>27</v>
       </c>
       <c r="B18" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C18" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D18" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F18" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J18" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K18" s="0" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0</v>
+      </c>
+      <c r="L18" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
         <v>28</v>
       </c>
       <c r="B19" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C19" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D19" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" s="0" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J19" s="0" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K19" s="0" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
         <v>29</v>
       </c>
       <c r="B20" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C20" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="0" t="n">
         <v>0</v>
@@ -2003,130 +2175,166 @@
       <c r="K20" s="0" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
         <v>30</v>
       </c>
       <c r="B21" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C21" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D21" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F21" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="0" t="n">
         <v>1</v>
       </c>
       <c r="J21" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" s="0" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
         <v>31</v>
       </c>
       <c r="B22" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C22" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D22" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F22" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" s="0" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" s="0" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
         <v>32</v>
       </c>
       <c r="B23" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C23" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D23" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F23" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="0" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J23" s="0" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="K23" s="0" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
         <v>33</v>
       </c>
       <c r="B24" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C24" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D24" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F24" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="0" t="n">
         <v>1</v>
@@ -2135,7 +2343,7 @@
         <v>1</v>
       </c>
       <c r="I24" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" s="0" t="n">
         <v>0</v>
@@ -2143,25 +2351,34 @@
       <c r="K24" s="0" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
         <v>34</v>
       </c>
       <c r="B25" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C25" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D25" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F25" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="0" t="n">
         <v>1</v>
@@ -2173,80 +2390,107 @@
         <v>1</v>
       </c>
       <c r="J25" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" s="0" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
         <v>35</v>
       </c>
       <c r="B26" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C26" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D26" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F26" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="0" t="n">
         <v>1</v>
       </c>
       <c r="H26" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" s="0" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
         <v>36</v>
       </c>
       <c r="B27" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C27" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D27" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F27" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" s="0" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J27" s="0" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K27" s="0" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="L27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2265,8 +2509,893 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:J27"/>
+  <sheetFormatPr defaultColWidth="10.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="5.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="5" style="0" width="10.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1024" style="0" width="8.36"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H2" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I2" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J2" s="0" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H3" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I3" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J3" s="0" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I4" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I5" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J5" s="0" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I6" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J6" s="0" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I7" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J7" s="0" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H8" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I8" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F9" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H9" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I9" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I10" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J10" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C11" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I11" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J11" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D12" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I12" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J12" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D13" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I13" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J13" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D14" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I14" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J14" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C15" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D15" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I15" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J15" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C16" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D16" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I16" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J16" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C17" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D17" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I17" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J17" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C18" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D18" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I18" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J18" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C19" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D19" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I19" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J19" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C20" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D20" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C21" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D21" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C22" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D22" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C23" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D23" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I23" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J23" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C24" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D24" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C25" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D25" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C26" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D26" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C27" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D27" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I27" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J27" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:P27"/>
-  <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.54296875" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="5.83"/>
   </cols>
@@ -2279,7 +3408,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E1" s="0" t="s">
         <v>2</v>
@@ -2294,7 +3423,7 @@
         <v>5</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J1" s="0" t="s">
         <v>6</v>
@@ -2312,10 +3441,10 @@
         <v>10</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
